--- a/RevGame_Client/配置表/增益与事件配置.xlsx
+++ b/RevGame_Client/配置表/增益与事件配置.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PrepBuffConfig" sheetId="1" r:id="R6e6a3b15080d4daf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleEventConfig" sheetId="2" r:id="R14341e5e2de941d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventRotationConfig" sheetId="3" r:id="Raa2d307db6c64eb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="4" r:id="R1b04e2301f5c4722"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PrepBuffConfig" sheetId="1" r:id="R7e5374bad79542db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleEventConfig" sheetId="2" r:id="Rb7c6a8adf27d4e89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventRotationConfig" sheetId="3" r:id="R095b0ee685ae449f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="4" r:id="Rc4a348f99a6545f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -674,7 +674,7 @@
         </x:is>
       </x:c>
       <x:c r="D6" s="4" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="E6" s="4" t="n"/>
       <x:c r="F6" s="4" t="n"/>
@@ -746,7 +746,7 @@
         </x:is>
       </x:c>
       <x:c r="D9" s="4" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="E9" s="4" t="n"/>
       <x:c r="F9" s="4" t="n"/>
@@ -818,7 +818,7 @@
         </x:is>
       </x:c>
       <x:c r="D12" s="4" t="n">
-        <x:v>0.2</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="E12" s="4" t="n"/>
       <x:c r="F12" s="4" t="n"/>
@@ -842,7 +842,7 @@
         </x:is>
       </x:c>
       <x:c r="D13" s="4" t="n">
-        <x:v>0.04</x:v>
+        <x:v>0.025</x:v>
       </x:c>
       <x:c r="E13" s="4" t="n"/>
       <x:c r="F13" s="4" t="n"/>
@@ -855,10 +855,8 @@
           <x:t xml:space="preserve">Shields</x:t>
         </x:is>
       </x:c>
-      <x:c r="B14" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">三重护盾</x:t>
-        </x:is>
+      <x:c r="B14" s="4" t="str">
+        <x:v>双重护盾</x:v>
       </x:c>
       <x:c r="C14" s="4" t="inlineStr">
         <x:is>
@@ -866,7 +864,7 @@
         </x:is>
       </x:c>
       <x:c r="D14" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E14" s="4" t="n"/>
       <x:c r="F14" s="4" t="n"/>
@@ -890,7 +888,7 @@
         </x:is>
       </x:c>
       <x:c r="D15" s="4" t="n">
-        <x:v>0.35</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="E15" s="4" t="n"/>
       <x:c r="F15" s="4" t="n"/>
@@ -914,7 +912,7 @@
         </x:is>
       </x:c>
       <x:c r="D16" s="4" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="E16" s="4" t="n"/>
       <x:c r="F16" s="4" t="n">
@@ -940,7 +938,7 @@
         </x:is>
       </x:c>
       <x:c r="D17" s="4" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="E17" s="4" t="n">
         <x:v>0.06</x:v>
@@ -990,7 +988,7 @@
         </x:is>
       </x:c>
       <x:c r="D19" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="E19" s="4" t="n"/>
       <x:c r="F19" s="4" t="n"/>
@@ -1145,7 +1143,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="4" t="n">
-        <x:v>0.1</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="E6" s="4" t="n"/>
     </x:row>
@@ -1164,10 +1162,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="4" t="n">
-        <x:v>0.2</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="E7" s="4" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.35</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
@@ -1240,7 +1238,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D11" s="4" t="n">
-        <x:v>0.12</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="E11" s="4" t="n"/>
     </x:row>
@@ -1255,7 +1253,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" t="n">
-        <x:v>0.15</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="E12" t="n">
         <x:v>5</x:v>
@@ -1272,7 +1270,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" t="n">
-        <x:v>0.15</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="E13" t="n">
         <x:v>5</x:v>
@@ -1289,7 +1287,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" t="n">
-        <x:v>0.1</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="E14" t="n">
         <x:v>5</x:v>
@@ -1306,7 +1304,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" t="n">
-        <x:v>0.15</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="E15" t="n">
         <x:v>5</x:v>
